--- a/marketing_forms/014_mario_form_2026_wedrive4u--marketing_forms.xlsx
+++ b/marketing_forms/014_mario_form_2026_wedrive4u--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>select_one_with_placeholder</t>
+          <t>select_one_with_placeholder_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Select One with Placeholder</t>
+          <t>Select One With Placeholder 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select One Without Label</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select Multiple Without Label</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select One With Label</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select Multiple With Label</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>select_one_with_label</t>
+          <t>select_one_with_label_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select One With Label 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>select_multiple_with_label</t>
+          <t>select_multiple_with_label_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select Multiple With Label 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option_1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option_2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option_3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one_with_placeholder_choices</t>
+          <t>select_one_with_placeholder_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1227,7 +1227,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one_with_placeholder_choices</t>
+          <t>select_one_with_placeholder_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1380,7 +1380,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one_with_label_choices</t>
+          <t>select_one_with_label_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1397,7 +1397,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one_with_label_choices</t>
+          <t>select_one_with_label_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1414,7 +1414,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple_with_label_choices</t>
+          <t>select_multiple_with_label_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1431,7 +1431,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple_with_label_choices</t>
+          <t>select_multiple_with_label_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
